--- a/Reporte_gastos/Gastos en Odoo 20260716.xlsx
+++ b/Reporte_gastos/Gastos en Odoo 20260716.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Valeria\Reportes\Reporte_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maval\Documents\Vale laburo\Castelli\Reportes\Reporte_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="6310"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15528" windowHeight="6312" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId3"/>
+    <pivotCache cacheId="70" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>EXPENSAS</t>
-  </si>
-  <si>
-    <t>PUBLICIDAD</t>
   </si>
   <si>
     <t>ALQUILER LOCALES</t>
@@ -243,15 +240,19 @@
   <si>
     <t>Suma de Importe</t>
   </si>
+  <si>
+    <t>FUMIGACION</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,13 +268,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -285,10 +305,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -305,11 +326,159 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -323,7 +492,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="PC" refreshedDate="46219.540062615742" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="220">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Valeria Levite" refreshedDate="46223.788344328706" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="220">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:H221" sheet="Sheet1"/>
   </cacheSource>
@@ -346,14 +515,14 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Descripción" numFmtId="0">
-      <sharedItems count="26">
+      <sharedItems count="27">
         <s v="EXPENSAS"/>
-        <s v="PUBLICIDAD"/>
         <s v="ALQUILER LOCALES"/>
         <s v="Servicio Eléctrico"/>
         <s v="GASTOS MEDICOS"/>
         <s v="GASTOS DE MANTENIMIENTO Y REPARACIONES"/>
         <s v="Servicio de Internet"/>
+        <s v="FUMIGACION"/>
         <s v="LIBRERIA"/>
         <s v="Servicio de Agua"/>
         <s v="ABL"/>
@@ -372,6 +541,7 @@
         <s v="CMV 01/2026"/>
         <s v="CMV 12-2025"/>
         <s v="Expensas AS SANTELMO 06-2026" u="1"/>
+        <s v="PUBLICIDAD" u="1"/>
         <s v="Expensas 06-2026 LU ST 1 y 2" u="1"/>
       </sharedItems>
     </cacheField>
@@ -464,7 +634,7 @@
   <r>
     <x v="3"/>
     <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-07-08T00:00:00"/>
     <n v="-1736485.35"/>
@@ -494,30 +664,10 @@
   <r>
     <x v="4"/>
     <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-07-06T00:00:00"/>
     <n v="-2358898.86"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="3"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="-82244.25"/>
-    <x v="0"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="-66242.19"/>
     <x v="0"/>
     <x v="0"/>
   </r>
@@ -527,6 +677,26 @@
     <x v="2"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-07-01T00:00:00"/>
+    <n v="-82244.25"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-07-01T00:00:00"/>
+    <n v="-66242.19"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-07-01T00:00:00"/>
     <n v="-570010.85"/>
     <x v="0"/>
     <x v="0"/>
@@ -534,7 +704,7 @@
   <r>
     <x v="6"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-30T00:00:00"/>
     <n v="-66800"/>
@@ -544,7 +714,7 @@
   <r>
     <x v="7"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-30T00:00:00"/>
     <n v="-66800"/>
@@ -554,7 +724,7 @@
   <r>
     <x v="1"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-30T00:00:00"/>
     <n v="-836060"/>
@@ -564,7 +734,7 @@
   <r>
     <x v="1"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-30T00:00:00"/>
     <n v="-909800"/>
@@ -574,7 +744,7 @@
   <r>
     <x v="7"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-30T00:00:00"/>
     <n v="-877200"/>
@@ -584,7 +754,7 @@
   <r>
     <x v="7"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-30T00:00:00"/>
     <n v="-536000"/>
@@ -594,17 +764,17 @@
   <r>
     <x v="3"/>
     <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
-    <x v="6"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-28T00:00:00"/>
+    <x v="5"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-07-01T00:00:00"/>
     <n v="-24609.93"/>
-    <x v="1"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
     <x v="5"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-22T00:00:00"/>
     <n v="-31800"/>
@@ -614,7 +784,7 @@
   <r>
     <x v="7"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-22T00:00:00"/>
     <n v="-15900"/>
@@ -624,7 +794,7 @@
   <r>
     <x v="5"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-22T00:00:00"/>
     <n v="-91800"/>
@@ -634,10 +804,310 @@
   <r>
     <x v="7"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-06-22T00:00:00"/>
     <n v="-45900"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="-58606.89"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="-82049.649999999994"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-19056.04"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-22994.639999999999"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-53248.68"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-22994.639999999999"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="WASSER ARMANDO HECTOR"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="-47553.72"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="WASSER ARMANDO HECTOR"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="-47553.72"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="8"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="-32848.980000000003"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="9"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="-690308.12"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="8"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="-522241.21"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="-482850.5"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="FIDEICOMISO LAGUNA OSCURA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-1002486.6"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-136188.79999999999"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-7325000"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-2407649.61"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-326619.98"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-2177466.54"/>
     <x v="1"/>
     <x v="0"/>
   </r>
@@ -646,19 +1116,669 @@
     <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
     <x v="2"/>
     <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-19T00:00:00"/>
-    <n v="-58606.89"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-30340.58"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-57000.46"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-10T00:00:00"/>
+    <n v="-511403.96"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="-56911"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="-56911"/>
     <x v="1"/>
     <x v="0"/>
   </r>
   <r>
     <x v="6"/>
     <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="-372568.23"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="-715965.54"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="MESATEL SA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-08T00:00:00"/>
+    <n v="-1079060"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="MESATEL SA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-08T00:00:00"/>
+    <n v="-2204956.64"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
     <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-19T00:00:00"/>
-    <n v="-82049.649999999994"/>
-    <x v="1"/>
+    <s v="MESATEL SA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-08T00:00:00"/>
+    <n v="-1241904.8700000001"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
+    <x v="5"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-07T00:00:00"/>
+    <n v="-35348.769999999997"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-05T00:00:00"/>
+    <n v="-184127.32"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-05T00:00:00"/>
+    <n v="-165714.59"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-05T00:00:00"/>
+    <n v="-1657145.89"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-04T00:00:00"/>
+    <n v="-56911"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="MARTINEZ VANESA ROSANA"/>
+    <x v="10"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="-20000"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="MARTINEZ VANESA ROSANA"/>
+    <x v="10"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="-20000"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GIORDANO JUAN CARLOS"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-31T00:00:00"/>
+    <n v="-49752.06"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="CHARKOWY, CARLOS IGNACIO"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-31T00:00:00"/>
+    <n v="-13223.14"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
+    <x v="5"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="-28289.27"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
+    <x v="5"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="-24129.759999999998"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="MESATEL SA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-26T00:00:00"/>
+    <n v="-2056151.52"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="MESATEL SA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-26T00:00:00"/>
+    <n v="-1079060"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="MESATEL SA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-26T00:00:00"/>
+    <n v="-1047092"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-50705"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-50705"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-50705"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="SEGURIDAD DENAPOLI S.R.L."/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-50705"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-42536.160000000003"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-22994.639999999999"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-53209.440000000002"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-22994.639999999999"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="MANOLIO MARIANO SERGIO"/>
+    <x v="6"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-42496.92"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-381156.89"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="8"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-29850.82"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="8"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-474575.79"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="11"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-622615.99"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="LABORALPRE"/>
+    <x v="3"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-61800"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-823472"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-411736"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-411736"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-411736"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-411736"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-1235208"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="CROSS ONA SRL"/>
+    <x v="12"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-21T00:00:00"/>
+    <n v="-411736"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-70272.36"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-35136.18"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-35136.18"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-35136.18"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-35136.18"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-105408.54"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Dolphine SAS"/>
+    <x v="7"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="-35136.18"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-136188.79999999999"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="CHECK CLIMATIZACION"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-135955.20000000001"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="ARRECH ALAN MAURICIO"/>
+    <x v="4"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="-120800"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="FIDEICOMISO LAGUNA OSCURA"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-14T00:00:00"/>
+    <n v="-923100"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="MAGECA S A"/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-13T00:00:00"/>
+    <n v="-7050000"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-11T00:00:00"/>
+    <n v="-54001.42"/>
+    <x v="2"/>
     <x v="0"/>
   </r>
   <r>
@@ -666,119 +1786,149 @@
     <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
     <x v="2"/>
     <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-19056.04"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
+    <d v="2026-05-11T00:00:00"/>
+    <n v="-28746.7"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
     <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-11T00:00:00"/>
+    <n v="-511403.96"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
     <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="1"/>
+    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-11T00:00:00"/>
+    <n v="-58711.23"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-08T00:00:00"/>
+    <n v="-184127.32"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-08T00:00:00"/>
+    <n v="-165714.59"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-08T00:00:00"/>
+    <n v="-1657145.89"/>
+    <x v="2"/>
     <x v="0"/>
   </r>
   <r>
     <x v="4"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="1"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-08T00:00:00"/>
+    <n v="-326619.98"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="1"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-08T00:00:00"/>
+    <n v="-2177466.54"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="FORTIN MAURE S. A."/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-06T00:00:00"/>
+    <n v="-2420500.2599999998"/>
+    <x v="2"/>
     <x v="0"/>
   </r>
   <r>
     <x v="6"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-22994.639999999999"/>
-    <x v="1"/>
+    <m/>
+    <x v="13"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-27581"/>
+    <x v="3"/>
     <x v="0"/>
   </r>
   <r>
     <x v="8"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="1"/>
+    <m/>
+    <x v="14"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-298257.44"/>
+    <x v="3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <m/>
+    <x v="15"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-671764.67"/>
+    <x v="3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <m/>
+    <x v="16"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-671764.67"/>
+    <x v="3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <m/>
+    <x v="17"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-1343529.34"/>
+    <x v="3"/>
     <x v="0"/>
   </r>
   <r>
     <x v="7"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-53248.68"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-22994.639999999999"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-18T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="WASSER ARMANDO HECTOR"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-17T00:00:00"/>
-    <n v="-47553.72"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="WASSER ARMANDO HECTOR"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-17T00:00:00"/>
-    <n v="-47553.72"/>
-    <x v="1"/>
+    <s v="MAGECA S A"/>
+    <x v="0"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-482850.5"/>
+    <x v="3"/>
     <x v="0"/>
   </r>
   <r>
@@ -786,19 +1936,9 @@
     <s v="MAGECA S A"/>
     <x v="8"/>
     <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-16T00:00:00"/>
-    <n v="-32848.980000000003"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="9"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-16T00:00:00"/>
-    <n v="-690308.12"/>
-    <x v="1"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-29615.17"/>
+    <x v="3"/>
     <x v="0"/>
   </r>
   <r>
@@ -806,539 +1946,9 @@
     <s v="MAGECA S A"/>
     <x v="8"/>
     <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-16T00:00:00"/>
-    <n v="-522241.21"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-16T00:00:00"/>
-    <n v="-482850.5"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="FIDEICOMISO LAGUNA OSCURA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-1002486.6"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-136188.79999999999"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-12T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-7325000"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-2407649.61"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="1"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-326619.98"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-2177466.54"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="3"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-30340.58"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-57000.46"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-10T00:00:00"/>
-    <n v="-511403.96"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-09T00:00:00"/>
-    <n v="-56911"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-09T00:00:00"/>
-    <n v="-56911"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-09T00:00:00"/>
-    <n v="-372568.23"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-09T00:00:00"/>
-    <n v="-715965.54"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="MESATEL SA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-08T00:00:00"/>
-    <n v="-1079060"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="MESATEL SA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-08T00:00:00"/>
-    <n v="-2204956.64"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="MESATEL SA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-08T00:00:00"/>
-    <n v="-1241904.8700000001"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
-    <x v="6"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-07T00:00:00"/>
-    <n v="-35348.769999999997"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-05T00:00:00"/>
-    <n v="-184127.32"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="1"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-05T00:00:00"/>
-    <n v="-165714.59"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-05T00:00:00"/>
-    <n v="-1657145.89"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-04T00:00:00"/>
-    <n v="-56911"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="MARTINEZ VANESA ROSANA"/>
-    <x v="10"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-01T00:00:00"/>
-    <n v="-20000"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="MARTINEZ VANESA ROSANA"/>
-    <x v="10"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-06-01T00:00:00"/>
-    <n v="-20000"/>
-    <x v="1"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GIORDANO JUAN CARLOS"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-31T00:00:00"/>
-    <n v="-49752.06"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="CHARKOWY, CARLOS IGNACIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-31T00:00:00"/>
-    <n v="-13223.14"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
-    <x v="6"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-29T00:00:00"/>
-    <n v="-28289.27"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
-    <x v="6"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-28T00:00:00"/>
-    <n v="-24129.759999999998"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="MESATEL SA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-26T00:00:00"/>
-    <n v="-2056151.52"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="MESATEL SA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-26T00:00:00"/>
-    <n v="-1079060"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="MESATEL SA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-26T00:00:00"/>
-    <n v="-1047092"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-50705"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-50705"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-50705"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-50705"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-42536.160000000003"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-22994.639999999999"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-53209.440000000002"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-22994.639999999999"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-42496.92"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-381156.89"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="8"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-29850.82"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="8"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-474575.79"/>
-    <x v="2"/>
+    <d v="2026-04-30T00:00:00"/>
+    <n v="-470829.46"/>
+    <x v="3"/>
     <x v="0"/>
   </r>
   <r>
@@ -1346,446 +1956,6 @@
     <s v="MAGECA S A"/>
     <x v="11"/>
     <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-622615.99"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="LABORALPRE"/>
-    <x v="4"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-61800"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-823472"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-411736"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-411736"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-411736"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-411736"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-1235208"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="CROSS ONA SRL"/>
-    <x v="12"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-21T00:00:00"/>
-    <n v="-411736"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-70272.36"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-35136.18"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-35136.18"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-35136.18"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-35136.18"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-105408.54"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="Dolphine SAS"/>
-    <x v="7"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-20T00:00:00"/>
-    <n v="-35136.18"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-136188.79999999999"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-135955.20000000001"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="ARRECH ALAN MAURICIO"/>
-    <x v="5"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-15T00:00:00"/>
-    <n v="-120800"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="FIDEICOMISO LAGUNA OSCURA"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-14T00:00:00"/>
-    <n v="-923100"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-13T00:00:00"/>
-    <n v="-7050000"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-11T00:00:00"/>
-    <n v="-54001.42"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="3"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-11T00:00:00"/>
-    <n v="-28746.7"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-11T00:00:00"/>
-    <n v="-511403.96"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-11T00:00:00"/>
-    <n v="-58711.23"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-08T00:00:00"/>
-    <n v="-184127.32"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="1"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-08T00:00:00"/>
-    <n v="-165714.59"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-08T00:00:00"/>
-    <n v="-1657145.89"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="1"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-08T00:00:00"/>
-    <n v="-326619.98"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-08T00:00:00"/>
-    <n v="-2177466.54"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="FORTIN MAURE S. A."/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-05-06T00:00:00"/>
-    <n v="-2420500.2599999998"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <m/>
-    <x v="13"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-27581"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <m/>
-    <x v="14"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-298257.44"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <m/>
-    <x v="15"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-671764.67"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <m/>
-    <x v="16"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-671764.67"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <m/>
-    <x v="17"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-1343529.34"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="0"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-482850.5"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="8"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-29615.17"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="8"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
-    <n v="-470829.46"/>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="MAGECA S A"/>
-    <x v="11"/>
-    <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-659144.55000000005"/>
     <x v="3"/>
@@ -1804,11 +1974,11 @@
   <r>
     <x v="3"/>
     <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
-    <x v="6"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-30T00:00:00"/>
+    <x v="5"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-01T00:00:00"/>
     <n v="-23314.06"/>
-    <x v="3"/>
+    <x v="2"/>
     <x v="0"/>
   </r>
   <r>
@@ -1834,7 +2004,7 @@
   <r>
     <x v="2"/>
     <s v="OKOS ENRIQUE CARMELO"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-141000"/>
@@ -1844,7 +2014,7 @@
   <r>
     <x v="7"/>
     <s v="CHARKOWY, CARLOS IGNACIO"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-159504.18"/>
@@ -1854,7 +2024,7 @@
   <r>
     <x v="0"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-79992"/>
@@ -1864,7 +2034,7 @@
   <r>
     <x v="6"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-79992"/>
@@ -1874,7 +2044,7 @@
   <r>
     <x v="8"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-80016"/>
@@ -1884,7 +2054,7 @@
   <r>
     <x v="0"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-80000"/>
@@ -1894,7 +2064,7 @@
   <r>
     <x v="4"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-160000"/>
@@ -1904,7 +2074,7 @@
   <r>
     <x v="6"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-160000"/>
@@ -1914,7 +2084,7 @@
   <r>
     <x v="8"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-160000"/>
@@ -1924,7 +2094,7 @@
   <r>
     <x v="7"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-160000"/>
@@ -1934,7 +2104,7 @@
   <r>
     <x v="2"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-30T00:00:00"/>
     <n v="-80000"/>
@@ -1944,7 +2114,7 @@
   <r>
     <x v="4"/>
     <s v="CHARKOWY, CARLOS IGNACIO"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-29T00:00:00"/>
     <n v="-38016.519999999997"/>
@@ -1954,7 +2124,7 @@
   <r>
     <x v="7"/>
     <s v="CHARKOWY, CARLOS IGNACIO"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-29T00:00:00"/>
     <n v="-38016.51"/>
@@ -1964,7 +2134,7 @@
   <r>
     <x v="2"/>
     <s v="PERTICARI Y CIA S.A."/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-29T00:00:00"/>
     <n v="-49123.43"/>
@@ -1974,17 +2144,17 @@
   <r>
     <x v="5"/>
     <s v="TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
-    <x v="6"/>
-    <s v="EL LUCERO CUERO"/>
-    <d v="2026-04-29T00:00:00"/>
+    <x v="5"/>
+    <s v="EL LUCERO CUERO"/>
+    <d v="2026-05-01T00:00:00"/>
     <n v="-28896.7"/>
-    <x v="3"/>
+    <x v="2"/>
     <x v="0"/>
   </r>
   <r>
     <x v="5"/>
     <s v="SANES JUAN MANUEL"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-28T00:00:00"/>
     <n v="-857200"/>
@@ -1994,7 +2164,7 @@
   <r>
     <x v="6"/>
     <s v="STINETWORK S.R.L."/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-24T00:00:00"/>
     <n v="-10719.9"/>
@@ -2004,7 +2174,7 @@
   <r>
     <x v="8"/>
     <s v="FIDEICOMISO LAGUNA OSCURA"/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-24T00:00:00"/>
     <n v="-923100"/>
@@ -2014,7 +2184,7 @@
   <r>
     <x v="0"/>
     <s v="SEGURIDAD DENAPOLI S.R.L."/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-24T00:00:00"/>
     <n v="-125098"/>
@@ -2024,7 +2194,7 @@
   <r>
     <x v="2"/>
     <s v="ARRECH ALAN MAURICIO"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-24T00:00:00"/>
     <n v="-2600800"/>
@@ -2034,7 +2204,7 @@
   <r>
     <x v="0"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-136136"/>
@@ -2044,7 +2214,7 @@
   <r>
     <x v="1"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-136136"/>
@@ -2054,7 +2224,7 @@
   <r>
     <x v="4"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-136136"/>
@@ -2064,7 +2234,7 @@
   <r>
     <x v="6"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-136136"/>
@@ -2074,7 +2244,7 @@
   <r>
     <x v="8"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-135184"/>
@@ -2084,7 +2254,7 @@
   <r>
     <x v="7"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-136136"/>
@@ -2094,7 +2264,7 @@
   <r>
     <x v="2"/>
     <s v="CHECK CLIMATIZACION"/>
-    <x v="5"/>
+    <x v="4"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-23T00:00:00"/>
     <n v="-136136"/>
@@ -2144,7 +2314,7 @@
   <r>
     <x v="6"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-38780"/>
@@ -2154,7 +2324,7 @@
   <r>
     <x v="7"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-48290"/>
@@ -2164,7 +2334,7 @@
   <r>
     <x v="5"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-20900"/>
@@ -2174,7 +2344,7 @@
   <r>
     <x v="3"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-20900"/>
@@ -2184,7 +2354,7 @@
   <r>
     <x v="0"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-38780"/>
@@ -2194,7 +2364,7 @@
   <r>
     <x v="1"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-38780"/>
@@ -2204,7 +2374,7 @@
   <r>
     <x v="4"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-38780"/>
@@ -2214,7 +2384,7 @@
   <r>
     <x v="8"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-38780"/>
@@ -2224,7 +2394,7 @@
   <r>
     <x v="2"/>
     <s v="MANOLIO MARIANO SERGIO"/>
-    <x v="5"/>
+    <x v="6"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-38780"/>
@@ -2234,7 +2404,7 @@
   <r>
     <x v="5"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-57800"/>
@@ -2244,7 +2414,7 @@
   <r>
     <x v="7"/>
     <s v="LABORALPRE"/>
-    <x v="4"/>
+    <x v="3"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-21T00:00:00"/>
     <n v="-57800"/>
@@ -2254,7 +2424,7 @@
   <r>
     <x v="7"/>
     <s v="MAGECA S A"/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-15T00:00:00"/>
     <n v="-6900000"/>
@@ -2274,7 +2444,7 @@
   <r>
     <x v="4"/>
     <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-2177466.54"/>
@@ -2304,7 +2474,7 @@
   <r>
     <x v="5"/>
     <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-511403.96"/>
@@ -2314,7 +2484,7 @@
   <r>
     <x v="6"/>
     <s v="GALERIA GENERAL GUEMES SOCIEDAD ANONIMA INMOBILIARIA S. A."/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-715965.54"/>
@@ -2334,7 +2504,7 @@
   <r>
     <x v="1"/>
     <s v="MESATEL SA"/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-1230248.2"/>
@@ -2344,7 +2514,7 @@
   <r>
     <x v="0"/>
     <s v="MESATEL SA"/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-2239640.96"/>
@@ -2354,7 +2524,7 @@
   <r>
     <x v="2"/>
     <s v="MESATEL SA"/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-1089870.3899999999"/>
@@ -2384,7 +2554,7 @@
   <r>
     <x v="3"/>
     <s v="FORTIN MAURE S. A."/>
-    <x v="2"/>
+    <x v="1"/>
     <s v="EL LUCERO CUERO"/>
     <d v="2026-04-10T00:00:00"/>
     <n v="-1557806.59"/>
@@ -2615,7 +2785,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="70" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:M15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0">
@@ -2635,9 +2805,9 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
-      <items count="27">
+      <items count="28">
         <item x="9"/>
-        <item x="2"/>
+        <item x="1"/>
         <item x="10"/>
         <item x="19"/>
         <item x="22"/>
@@ -2648,20 +2818,21 @@
         <item x="14"/>
         <item x="16"/>
         <item x="15"/>
-        <item m="1" x="25"/>
+        <item m="1" x="26"/>
         <item m="1" x="24"/>
-        <item x="5"/>
         <item x="4"/>
+        <item x="3"/>
         <item x="12"/>
         <item x="7"/>
         <item x="13"/>
         <item x="20"/>
         <item x="21"/>
         <item x="11"/>
-        <item x="1"/>
+        <item m="1" x="25"/>
         <item x="8"/>
+        <item x="5"/>
+        <item x="2"/>
         <item x="6"/>
-        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2748,9 +2919,6 @@
       <x v="17"/>
     </i>
     <i>
-      <x v="22"/>
-    </i>
-    <i>
       <x v="23"/>
     </i>
     <i>
@@ -2758,6 +2926,9 @@
     </i>
     <i>
       <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
     </i>
     <i t="grand">
       <x/>
@@ -2770,6 +2941,257 @@
   <dataFields count="1">
     <dataField name="Suma de Importe" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="20">
+    <format dxfId="19">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="4"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="5"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="7"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="2">
+            <x v="8"/>
+            <x v="9"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="5"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="7"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="5"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1">
+            <x v="5"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="9">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="26"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3066,95 +3488,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
-    <col min="6" max="6" width="40.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="41.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="6">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>-1241904.8700000001</v>
       </c>
       <c r="D6" s="7">
@@ -3162,148 +3584,164 @@
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7">
-        <v>-235363.12</v>
+        <v>-192866.2</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7">
+      <c r="J6" s="8">
         <v>-35348.769999999997</v>
       </c>
-      <c r="L6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="8">
+        <v>-42496.92</v>
+      </c>
       <c r="M6" s="7">
-        <v>-1532616.7600000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+        <v>-1532616.76</v>
+      </c>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="7">
-        <v>-1657145.89</v>
+      <c r="C7" s="8">
+        <v>-1822860.48</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>-184127.32</v>
       </c>
-      <c r="F7" s="7">
-        <v>-22994.639999999999</v>
-      </c>
+      <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7">
         <v>-47553.72</v>
       </c>
-      <c r="I7" s="7">
-        <v>-165714.59</v>
-      </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7">
-        <v>-24609.93</v>
-      </c>
-      <c r="L7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8">
+        <v>-24129.759999999998</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8">
+        <v>-22994.639999999999</v>
+      </c>
       <c r="M7" s="7">
-        <v>-2102146.09</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <v>-2101665.92</v>
+      </c>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="7">
+        <v>21</v>
+      </c>
+      <c r="B8" s="8">
         <v>-690308.12</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>-7325000</v>
       </c>
       <c r="D8" s="7"/>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>-482850.5</v>
       </c>
       <c r="F8" s="7">
-        <v>-1602637.48</v>
+        <v>-1549388.8</v>
       </c>
       <c r="G8" s="7">
         <v>-128600</v>
       </c>
       <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7">
+      <c r="I8" s="10">
         <v>-555090.19000000006</v>
       </c>
+      <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="L8" s="8">
+        <v>-53248.68</v>
+      </c>
       <c r="M8" s="7">
         <v>-10784486.290000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>-1002486.6</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7">
-        <v>-178452.12</v>
+        <v>-135955.20000000001</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="L9" s="8">
+        <v>-42496.92</v>
+      </c>
       <c r="M9" s="7">
         <v>-1180938.72</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>-589066.89</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>-57000.46</v>
       </c>
-      <c r="F10" s="7">
-        <v>-22994.639999999999</v>
-      </c>
+      <c r="F10" s="7"/>
       <c r="G10" s="7">
         <v>-123600</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7">
+      <c r="J10" s="8">
+        <v>-28289.27</v>
+      </c>
+      <c r="K10" s="8">
         <v>-30340.58</v>
       </c>
+      <c r="L10" s="8">
+        <v>-22994.639999999999</v>
+      </c>
       <c r="M10" s="7">
-        <v>-823002.57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+        <v>-851291.84</v>
+      </c>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>-798015.19000000006</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>-372568.23</v>
       </c>
       <c r="F11" s="7">
-        <v>-235363.12</v>
+        <v>-192866.2</v>
       </c>
       <c r="G11" s="7">
         <v>-66800</v>
@@ -3312,52 +3750,58 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="L11" s="8">
+        <v>-42496.92</v>
+      </c>
       <c r="M11" s="7">
-        <v>-1472746.54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>-1472746.5399999998</v>
+      </c>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="7">
-        <v>-2177466.54</v>
+      <c r="C12" s="8">
+        <v>-2504086.52</v>
       </c>
       <c r="D12" s="7">
         <v>-20000</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <v>-2407649.61</v>
       </c>
       <c r="F12" s="7">
-        <v>-178452.12</v>
+        <v>-135955.20000000001</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="7">
-        <v>-326619.98</v>
-      </c>
+      <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="L12" s="8">
+        <v>-42496.92</v>
+      </c>
       <c r="M12" s="7">
         <v>-5110188.25</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>-1079060</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7">
-        <v>-1981223.1199999999</v>
+        <v>-1938726.2</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7">
@@ -3366,43 +3810,51 @@
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="L13" s="8">
+        <v>-42496.92</v>
+      </c>
       <c r="M13" s="7">
         <v>-3107836.8400000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>-2204956.64</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7">
-        <v>-178452.12</v>
+        <v>-135955.20000000001</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="L14" s="8">
+        <v>-42496.92</v>
+      </c>
       <c r="M14" s="7">
         <v>-2383408.7600000002</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="7">
         <v>-690308.12</v>
       </c>
       <c r="C15" s="7">
-        <v>-18075102.620000001</v>
+        <v>-18567437.189999998</v>
       </c>
       <c r="D15" s="7">
         <v>-40000</v>
@@ -3411,7 +3863,7 @@
         <v>-3504196.12</v>
       </c>
       <c r="F15" s="7">
-        <v>-4635932.4799999995</v>
+        <v>-4281713</v>
       </c>
       <c r="G15" s="7">
         <v>-319000</v>
@@ -3420,20 +3872,54 @@
         <v>-95107.44</v>
       </c>
       <c r="I15" s="7">
-        <v>-492334.56999999995</v>
+        <v>-555090.19000000006</v>
       </c>
       <c r="J15" s="7">
-        <v>-555090.19000000006</v>
+        <v>-87767.8</v>
       </c>
       <c r="K15" s="7">
-        <v>-59958.7</v>
+        <v>-30340.58</v>
       </c>
       <c r="L15" s="7">
-        <v>-30340.58</v>
+        <v>-354219.47999999992</v>
       </c>
       <c r="M15" s="7">
-        <v>-28497370.820000004</v>
-      </c>
+        <v>-28525179.920000002</v>
+      </c>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3442,14 +3928,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H221"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="30.7265625" customWidth="1"/>
+    <col min="1" max="7" width="30.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3469,13 +3954,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -3499,7 +3984,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -3523,7 +4008,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -3547,7 +4032,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3573,7 +4058,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3599,7 +4084,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3607,7 +4092,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -3625,9 +4110,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
@@ -3651,9 +4136,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>11</v>
@@ -3677,15 +4162,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -3703,15 +4188,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
@@ -3729,12 +4214,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>12</v>
@@ -3755,15 +4240,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -3781,15 +4266,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -3807,15 +4292,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -3833,15 +4318,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
@@ -3859,15 +4344,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>7</v>
@@ -3885,15 +4370,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -3911,15 +4396,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
@@ -3937,41 +4422,41 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="3">
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="F20" s="4">
         <v>-24609.93</v>
       </c>
       <c r="G20" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -3989,15 +4474,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -4015,15 +4500,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>7</v>
@@ -4041,15 +4526,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>7</v>
@@ -4067,15 +4552,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -4093,15 +4578,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
@@ -4119,15 +4604,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>7</v>
@@ -4145,15 +4630,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -4171,15 +4656,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>7</v>
@@ -4197,15 +4682,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>7</v>
@@ -4223,15 +4708,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>7</v>
@@ -4249,15 +4734,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
@@ -4275,15 +4760,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>7</v>
@@ -4301,15 +4786,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
@@ -4327,15 +4812,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>7</v>
@@ -4353,15 +4838,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>7</v>
@@ -4379,15 +4864,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>7</v>
@@ -4405,15 +4890,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -4431,15 +4916,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>7</v>
@@ -4457,15 +4942,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>7</v>
@@ -4483,15 +4968,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>7</v>
@@ -4509,12 +4994,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>12</v>
@@ -4535,15 +5020,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>7</v>
@@ -4561,15 +5046,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>7</v>
@@ -4587,15 +5072,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>7</v>
@@ -4613,15 +5098,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
@@ -4639,15 +5124,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>7</v>
@@ -4665,15 +5150,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>7</v>
@@ -4691,15 +5176,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>7</v>
@@ -4717,15 +5202,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>7</v>
@@ -4743,15 +5228,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>7</v>
@@ -4769,9 +5254,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>11</v>
@@ -4795,9 +5280,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>11</v>
@@ -4821,15 +5306,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
@@ -4847,15 +5332,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>7</v>
@@ -4873,12 +5358,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>12</v>
@@ -4899,15 +5384,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>7</v>
@@ -4925,15 +5410,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>7</v>
@@ -4951,15 +5436,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>7</v>
@@ -4977,12 +5462,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>12</v>
@@ -5003,15 +5488,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>7</v>
@@ -5029,15 +5514,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>7</v>
@@ -5055,15 +5540,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>7</v>
@@ -5081,15 +5566,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>7</v>
@@ -5107,15 +5592,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>7</v>
@@ -5133,7 +5618,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>10</v>
       </c>
@@ -5159,7 +5644,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>10</v>
       </c>
@@ -5185,7 +5670,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>10</v>
       </c>
@@ -5193,7 +5678,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -5211,15 +5696,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>7</v>
@@ -5237,15 +5722,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -5263,15 +5748,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>7</v>
@@ -5289,15 +5774,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>7</v>
@@ -5315,15 +5800,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>7</v>
@@ -5331,7 +5816,7 @@
       <c r="E73" s="3">
         <v>46173</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="11">
         <v>-13223.14</v>
       </c>
       <c r="G73" s="2">
@@ -5341,67 +5826,67 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D74" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E74" s="3">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="F74" s="4">
         <v>-28289.27</v>
       </c>
       <c r="G74" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H74">
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D75" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E75" s="3">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="F75" s="4">
         <v>-24129.759999999998</v>
       </c>
       <c r="G75" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H75">
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>7</v>
@@ -5419,15 +5904,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>7</v>
@@ -5445,15 +5930,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>7</v>
@@ -5471,15 +5956,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>7</v>
@@ -5497,15 +5982,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>7</v>
@@ -5523,15 +6008,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>7</v>
@@ -5549,15 +6034,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>7</v>
@@ -5575,15 +6060,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -5601,15 +6086,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>7</v>
@@ -5627,15 +6112,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>7</v>
@@ -5653,15 +6138,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>7</v>
@@ -5679,15 +6164,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>7</v>
@@ -5705,15 +6190,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>7</v>
@@ -5731,15 +6216,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>7</v>
@@ -5757,15 +6242,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>7</v>
@@ -5783,15 +6268,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>7</v>
@@ -5809,12 +6294,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>12</v>
@@ -5835,15 +6320,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>7</v>
@@ -5861,15 +6346,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>7</v>
@@ -5887,15 +6372,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>7</v>
@@ -5913,15 +6398,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>7</v>
@@ -5939,15 +6424,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>7</v>
@@ -5965,15 +6450,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>7</v>
@@ -5991,15 +6476,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>7</v>
@@ -6017,15 +6502,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
@@ -6043,15 +6528,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>7</v>
@@ -6069,15 +6554,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>7</v>
@@ -6095,15 +6580,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>7</v>
@@ -6121,15 +6606,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>7</v>
@@ -6147,15 +6632,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>7</v>
@@ -6173,15 +6658,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>7</v>
@@ -6199,15 +6684,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>7</v>
@@ -6225,15 +6710,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>7</v>
@@ -6251,15 +6736,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>7</v>
@@ -6277,15 +6762,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -6303,15 +6788,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -6329,15 +6814,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -6355,15 +6840,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>7</v>
@@ -6381,15 +6866,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>7</v>
@@ -6407,15 +6892,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>7</v>
@@ -6433,15 +6918,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>7</v>
@@ -6459,15 +6944,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>7</v>
@@ -6485,15 +6970,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -6511,15 +6996,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>7</v>
@@ -6537,15 +7022,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>7</v>
@@ -6563,15 +7048,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C121" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>7</v>
@@ -6589,15 +7074,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>7</v>
@@ -6615,15 +7100,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C123" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>7</v>
@@ -6641,12 +7126,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>12</v>
@@ -6667,7 +7152,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>10</v>
       </c>
@@ -6693,7 +7178,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>10</v>
       </c>
@@ -6719,7 +7204,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -6727,7 +7212,7 @@
         <v>11</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>7</v>
@@ -6745,9 +7230,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>11</v>
@@ -6771,15 +7256,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>7</v>
@@ -6797,9 +7282,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>11</v>
@@ -6823,13 +7308,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>7</v>
@@ -6847,13 +7332,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -6871,13 +7356,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>7</v>
@@ -6895,13 +7380,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>7</v>
@@ -6919,13 +7404,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>7</v>
@@ -6943,12 +7428,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>12</v>
@@ -6969,15 +7454,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>7</v>
@@ -6995,15 +7480,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B138" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>7</v>
@@ -7021,15 +7506,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>7</v>
@@ -7047,13 +7532,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>7</v>
@@ -7071,41 +7556,41 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D141" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E141" s="3">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="F141" s="4">
         <v>-23314.06</v>
       </c>
       <c r="G141" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H141">
         <v>2026</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>7</v>
@@ -7123,15 +7608,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>7</v>
@@ -7149,15 +7634,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>7</v>
@@ -7175,15 +7660,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
@@ -7191,7 +7676,7 @@
       <c r="E145" s="3">
         <v>46142</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="11">
         <v>-159504.18</v>
       </c>
       <c r="G145" s="2">
@@ -7201,15 +7686,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -7227,15 +7712,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>7</v>
@@ -7253,15 +7738,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>7</v>
@@ -7279,15 +7764,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>7</v>
@@ -7305,15 +7790,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>7</v>
@@ -7331,15 +7816,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>7</v>
@@ -7357,15 +7842,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>7</v>
@@ -7383,15 +7868,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>7</v>
@@ -7409,15 +7894,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>7</v>
@@ -7435,15 +7920,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>7</v>
@@ -7451,7 +7936,7 @@
       <c r="E155" s="3">
         <v>46141</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="11">
         <v>-38016.519999999997</v>
       </c>
       <c r="G155" s="2">
@@ -7461,15 +7946,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
@@ -7477,7 +7962,7 @@
       <c r="E156" s="3">
         <v>46141</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="11">
         <v>-38016.51</v>
       </c>
       <c r="G156" s="2">
@@ -7487,15 +7972,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>7</v>
@@ -7513,41 +7998,41 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D158" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E158" s="3">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="F158" s="4">
         <v>-28896.7</v>
       </c>
       <c r="G158" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H158">
         <v>2026</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>7</v>
@@ -7565,15 +8050,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>7</v>
@@ -7591,15 +8076,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>7</v>
@@ -7617,15 +8102,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>7</v>
@@ -7643,15 +8128,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>7</v>
@@ -7669,15 +8154,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>7</v>
@@ -7695,15 +8180,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>7</v>
@@ -7721,15 +8206,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>7</v>
@@ -7747,15 +8232,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>7</v>
@@ -7773,15 +8258,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>7</v>
@@ -7799,15 +8284,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>7</v>
@@ -7825,15 +8310,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>7</v>
@@ -7851,15 +8336,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>7</v>
@@ -7877,15 +8362,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>7</v>
@@ -7903,15 +8388,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>7</v>
@@ -7929,15 +8414,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
@@ -7955,15 +8440,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>7</v>
@@ -7981,15 +8466,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>7</v>
@@ -8007,15 +8492,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>7</v>
@@ -8033,15 +8518,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>7</v>
@@ -8059,15 +8544,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>7</v>
@@ -8085,15 +8570,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>7</v>
@@ -8111,15 +8596,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>7</v>
@@ -8137,15 +8622,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>7</v>
@@ -8163,15 +8648,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>7</v>
@@ -8189,15 +8674,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>7</v>
@@ -8215,15 +8700,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>7</v>
@@ -8241,15 +8726,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>7</v>
@@ -8267,9 +8752,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>11</v>
@@ -8293,15 +8778,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>7</v>
@@ -8319,15 +8804,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C189" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>7</v>
@@ -8345,12 +8830,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>12</v>
@@ -8371,15 +8856,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C191" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>7</v>
@@ -8397,15 +8882,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>7</v>
@@ -8423,12 +8908,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>12</v>
@@ -8449,15 +8934,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>7</v>
@@ -8475,15 +8960,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>7</v>
@@ -8501,15 +8986,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>7</v>
@@ -8527,7 +9012,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>10</v>
       </c>
@@ -8553,7 +9038,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>10</v>
       </c>
@@ -8579,7 +9064,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>10</v>
       </c>
@@ -8587,7 +9072,7 @@
         <v>11</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>7</v>
@@ -8605,9 +9090,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>11</v>
@@ -8631,15 +9116,15 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>7</v>
@@ -8657,13 +9142,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>7</v>
@@ -8681,13 +9166,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>7</v>
@@ -8705,13 +9190,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B204" s="2"/>
       <c r="C204" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>7</v>
@@ -8729,13 +9214,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>7</v>
@@ -8753,13 +9238,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B206" s="2"/>
       <c r="C206" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>7</v>
@@ -8777,13 +9262,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B207" s="2"/>
       <c r="C207" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>7</v>
@@ -8801,13 +9286,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B208" s="2"/>
       <c r="C208" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>7</v>
@@ -8825,13 +9310,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>7</v>
@@ -8849,13 +9334,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B210" s="2"/>
       <c r="C210" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>7</v>
@@ -8873,13 +9358,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -8897,13 +9382,13 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B212" s="2"/>
       <c r="C212" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>7</v>
@@ -8921,13 +9406,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B213" s="2"/>
       <c r="C213" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>7</v>
@@ -8945,13 +9430,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B214" s="2"/>
       <c r="C214" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>7</v>
@@ -8969,13 +9454,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B215" s="2"/>
       <c r="C215" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>7</v>
@@ -8993,13 +9478,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B216" s="2"/>
       <c r="C216" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>7</v>
@@ -9017,13 +9502,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>7</v>
@@ -9041,13 +9526,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B218" s="2"/>
       <c r="C218" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>7</v>
@@ -9065,13 +9550,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B219" s="2"/>
       <c r="C219" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>7</v>
@@ -9089,13 +9574,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B220" s="2"/>
       <c r="C220" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>7</v>
@@ -9113,13 +9598,13 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B221" s="2"/>
       <c r="C221" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>7</v>
@@ -9138,18 +9623,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G221">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="LUCERO RECOLETA COMPRA"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="ALQUILER LOCALES"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G221"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>